--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486661_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486661_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9391</v>
+        <v>7.2522</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9</v>
+        <v>3.4863</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0391</v>
+        <v>3.7659</v>
       </c>
       <c r="G2" t="n">
         <v>3.8512</v>
@@ -610,13 +610,13 @@
         <v>1.7377</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8868</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1029</v>
+        <v>0.6892</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7839</v>
+        <v>0.5107</v>
       </c>
       <c r="V2" t="n">
         <v>0.6565</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. MUKENDI KABANGA</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1665</v>
+        <v>5.8412</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6668</v>
+        <v>3.2905</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4997</v>
+        <v>2.5507</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3235</v>
+        <v>1.0661</v>
       </c>
       <c r="H3" t="n">
-        <v>5.0696</v>
+        <v>1.1384</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7461</v>
+        <v>-0.0723</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1798</v>
+        <v>1.3016</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1391</v>
+        <v>0.725</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0407</v>
+        <v>0.5766</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8563</v>
+        <v>-0.2355</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.06950000000000001</v>
+        <v>0.4134</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.6489</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7723</v>
+        <v>2.1239</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1239</v>
+        <v>-0.1931</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3515</v>
+        <v>2.3169</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7585</v>
+        <v>0.5241</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2407</v>
+        <v>0.0548</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5177</v>
+        <v>0.4693</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8568</v>
+        <v>2.1271</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3701</v>
+        <v>2.1271</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>G. MUKENDI KABANGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0635</v>
+        <v>5.5115</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4631</v>
+        <v>5.6325</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6004</v>
+        <v>-0.1211</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0661</v>
+        <v>4.3235</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1384</v>
+        <v>5.0696</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0723</v>
+        <v>-0.7461</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3016</v>
+        <v>5.1798</v>
       </c>
       <c r="K4" t="n">
-        <v>0.725</v>
+        <v>5.1391</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5766</v>
+        <v>0.0407</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2355</v>
+        <v>-0.8563</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4134</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6489</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1239</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1931</v>
+        <v>-2.1239</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3169</v>
+        <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2536</v>
+        <v>1.1034</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7725</v>
+        <v>0.2065</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5189</v>
+        <v>0.8969</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1271</v>
+        <v>0.8568</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1271</v>
+        <v>2.3701</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3886</v>
+        <v>4.9638</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9855</v>
+        <v>3.0889</v>
       </c>
       <c r="F5" t="n">
-        <v>1.403</v>
+        <v>1.8748</v>
       </c>
       <c r="G5" t="n">
         <v>3.0537</v>
@@ -844,13 +844,13 @@
         <v>1.7377</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2098</v>
+        <v>0.3655</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0273</v>
+        <v>0.1307</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.237</v>
+        <v>0.2348</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6771</v>
+        <v>3.9584</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0382</v>
+        <v>3.245</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6389</v>
+        <v>0.7134</v>
       </c>
       <c r="G6" t="n">
         <v>3.1195</v>
@@ -922,13 +922,13 @@
         <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1601</v>
+        <v>0.4415</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4416</v>
+        <v>-0.2347</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6017</v>
+        <v>0.6762</v>
       </c>
       <c r="V6" t="n">
         <v>1.5559</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9202</v>
+        <v>2.9821</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6452</v>
+        <v>0.9555</v>
       </c>
       <c r="F7" t="n">
-        <v>2.275</v>
+        <v>2.0267</v>
       </c>
       <c r="G7" t="n">
         <v>2.4208</v>
@@ -1000,13 +1000,13 @@
         <v>2.1239</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8276</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0273</v>
+        <v>0.3376</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8003</v>
+        <v>0.552</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3282</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1173</v>
+        <v>2.8579</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9896</v>
+        <v>1.5067</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1278</v>
+        <v>1.3512</v>
       </c>
       <c r="G8" t="n">
         <v>0.9035</v>
@@ -1078,13 +1078,13 @@
         <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4579</v>
+        <v>0.2827</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0553</v>
+        <v>0.4618</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4026</v>
+        <v>-0.1791</v>
       </c>
       <c r="V8" t="n">
         <v>0.8995</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3585</v>
+        <v>1.6439</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.453</v>
+        <v>-1.1427</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8114</v>
+        <v>2.7866</v>
       </c>
       <c r="G9" t="n">
         <v>1.1293</v>
@@ -1156,13 +1156,13 @@
         <v>0.9654</v>
       </c>
       <c r="S9" t="n">
-        <v>0.094</v>
+        <v>0.3795</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4416</v>
+        <v>-0.1313</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5356</v>
+        <v>0.5108</v>
       </c>
       <c r="V9" t="n">
         <v>0.3282</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>R. ACIU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1236</v>
+        <v>0.5584</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1274</v>
+        <v>-0.0552</v>
       </c>
       <c r="F10" t="n">
-        <v>2.251</v>
+        <v>0.6137</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6647</v>
+        <v>0.4825</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1793</v>
+        <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5147</v>
+        <v>0.2826</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9418</v>
+        <v>0.0621</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7661</v>
+        <v>0.0621</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8243</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7228</v>
+        <v>0.4205</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4132</v>
+        <v>0.1379</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3096</v>
+        <v>0.2826</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9308</v>
+        <v>0.1931</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.0546</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1239</v>
+        <v>0.1931</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2892</v>
+        <v>-0.1172</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9854</v>
+        <v>-0.1173</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3038</v>
+        <v>0.0001</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. ACIU</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.455</v>
+        <v>0.1309</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1587</v>
+        <v>-2.3685</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6137</v>
+        <v>2.4994</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4825</v>
+        <v>1.6647</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2</v>
+        <v>3.1793</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2826</v>
+        <v>-1.5147</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0621</v>
+        <v>0.9418</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0621</v>
+        <v>2.7661</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.8243</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4205</v>
+        <v>0.7228</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1379</v>
+        <v>0.4132</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2826</v>
+        <v>0.3096</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1931</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.0546</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1931</v>
+        <v>2.1239</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2206</v>
+        <v>1.2964</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2207</v>
+        <v>0.7443</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0001</v>
+        <v>0.5521</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2913</v>
+        <v>-4.7824</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1578</v>
+        <v>-3.8476</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1335</v>
+        <v>-0.9348</v>
       </c>
       <c r="G12" t="n">
         <v>-3.9451</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2537</v>
+        <v>0.2552</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3864</v>
+        <v>-0.0761</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1327</v>
+        <v>0.3313</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8995</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>30.9181</v>
+        <v>30.91789999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>13.7915</v>
+        <v>13.7914</v>
       </c>
       <c r="F13" t="n">
         <v>17.1265</v>
@@ -1438,7 +1438,7 @@
         <v>17.2447</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8248</v>
+        <v>0.8248000000000004</v>
       </c>
       <c r="J13" t="n">
         <v>18.0457</v>
@@ -1456,10 +1456,10 @@
         <v>3.099</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.0754</v>
+        <v>-3.075400000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>1.930699999999999</v>
+        <v>1.9307</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.5157</v>
@@ -1468,16 +1468,16 @@
         <v>15.4463</v>
       </c>
       <c r="S13" t="n">
-        <v>6.6206</v>
+        <v>6.620699999999999</v>
       </c>
       <c r="T13" t="n">
         <v>2.0655</v>
       </c>
       <c r="U13" t="n">
-        <v>4.555099999999999</v>
+        <v>4.5551</v>
       </c>
       <c r="V13" t="n">
-        <v>4.296800000000001</v>
+        <v>4.2968</v>
       </c>
       <c r="W13" t="n">
         <v>7.1957</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4858</v>
+        <v>3.0555</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5245</v>
+        <v>4.3176</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0387</v>
+        <v>-1.2622</v>
       </c>
       <c r="G14" t="n">
         <v>1.7326</v>
@@ -1546,13 +1546,13 @@
         <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2042</v>
+        <v>-0.6345</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.8142</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4032</v>
+        <v>0.1797</v>
       </c>
       <c r="V14" t="n">
         <v>1.1851</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8147</v>
+        <v>-0.5678</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2224</v>
+        <v>-1.3259</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4078</v>
+        <v>0.7581</v>
       </c>
       <c r="G15" t="n">
         <v>-0.285</v>
@@ -1624,13 +1624,13 @@
         <v>0.7723</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3366</v>
+        <v>-0.0897</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0273</v>
+        <v>-0.0761</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3639</v>
+        <v>-0.0136</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8459</v>
+        <v>-0.7343</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3414</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1873</v>
+        <v>-1.386</v>
       </c>
       <c r="G16" t="n">
         <v>0.7819</v>
@@ -1702,13 +1702,13 @@
         <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.215</v>
+        <v>-0.1034</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6347</v>
+        <v>-0.3244</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4196</v>
+        <v>0.221</v>
       </c>
       <c r="V16" t="n">
         <v>-1.7989</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5261</v>
+        <v>-0.9041</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4</v>
+        <v>-2.0897</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8739</v>
+        <v>1.1856</v>
       </c>
       <c r="G17" t="n">
         <v>-1.4763</v>
@@ -1780,13 +1780,13 @@
         <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0152</v>
+        <v>-0.3932</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7174</v>
+        <v>-0.4071</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2978</v>
+        <v>0.0139</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8339</v>
+        <v>-1.9139</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4299</v>
+        <v>-1.6368</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4039</v>
+        <v>-0.2771</v>
       </c>
       <c r="G18" t="n">
         <v>-3.4034</v>
@@ -1858,13 +1858,13 @@
         <v>1.7377</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2373</v>
+        <v>-0.3174</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5522</v>
+        <v>-0.759</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3148</v>
+        <v>0.4416</v>
       </c>
       <c r="V18" t="n">
         <v>1.2277</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BIURRUN SANTAMARIA</t>
+          <t>J. HERNÁNDEZ TRUJILLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8359</v>
+        <v>-3.3125</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1511</v>
+        <v>0.2972</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6848</v>
+        <v>-3.6098</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9171</v>
+        <v>0.0617</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0626</v>
+        <v>-0.3317</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8545</v>
+        <v>0.3934</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1251</v>
+        <v>2.5112</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0414</v>
+        <v>1.3243</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0837</v>
+        <v>1.1869</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0422</v>
+        <v>-2.4495</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1039</v>
+        <v>-1.656</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9382</v>
+        <v>-0.7935</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1585</v>
+        <v>-1.3515</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8881</v>
+        <v>-1.2897</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8823</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0058</v>
+        <v>-0.4272</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2277</v>
+        <v>-2.0845</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2277</v>
+        <v>-2.0845</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. HERNÁNDEZ TRUJILLO</t>
+          <t>A. BIURRUN SANTAMARIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4282</v>
+        <v>-3.7585</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2199</v>
+        <v>-0.875</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.2084</v>
+        <v>-2.8835</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0617</v>
+        <v>-1.9171</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3317</v>
+        <v>-1.0626</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3934</v>
+        <v>-0.8545</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5112</v>
+        <v>0.1251</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3243</v>
+        <v>0.0414</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1869</v>
+        <v>0.0837</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4495</v>
+        <v>-2.0422</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.656</v>
+        <v>-1.1039</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7935</v>
+        <v>-0.9382</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3515</v>
+        <v>-1.1585</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.4054</v>
+        <v>-0.0345</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3796</v>
+        <v>0.1584</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0259</v>
+        <v>-0.1928</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.0845</v>
+        <v>-1.2277</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.0845</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.999</v>
+        <v>-4.9797</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4305</v>
+        <v>-4.6374</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5685</v>
+        <v>-0.3424</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4202</v>
@@ -2092,13 +2092,13 @@
         <v>1.9308</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8331</v>
+        <v>-0.8138</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3869</v>
+        <v>-0.5937</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4462</v>
+        <v>-0.2201</v>
       </c>
       <c r="V21" t="n">
         <v>0.5712</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2055</v>
+        <v>-6.1752</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1193</v>
+        <v>-4.3262</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0862</v>
+        <v>-1.849</v>
       </c>
       <c r="G22" t="n">
         <v>-4.2165</v>
@@ -2170,13 +2170,13 @@
         <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3752</v>
+        <v>-0.3449</v>
       </c>
       <c r="T22" t="n">
-        <v>0.11</v>
+        <v>-0.0968</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4852</v>
+        <v>-0.248</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2277</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.9145</v>
+        <v>-10.2484</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.019299999999999</v>
+        <v>-7.5022</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8952</v>
+        <v>-2.7462</v>
       </c>
       <c r="G23" t="n">
         <v>-6.9272</v>
@@ -2248,13 +2248,13 @@
         <v>2.1239</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8868</v>
+        <v>-1.2207</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2968</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5899</v>
+        <v>-0.4409</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9421</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-30.9179</v>
+        <v>-29.5389</v>
       </c>
       <c r="E24" t="n">
-        <v>-17.1265</v>
+        <v>-17.1267</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.7913</v>
+        <v>-12.4125</v>
       </c>
       <c r="G24" t="n">
         <v>-18.0695</v>
@@ -2296,7 +2296,7 @@
         <v>-17.2449</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8248</v>
+        <v>-0.8247999999999995</v>
       </c>
       <c r="J24" t="n">
         <v>-0.02369999999999983</v>
@@ -2326,13 +2326,13 @@
         <v>13.5154</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.6207</v>
+        <v>-5.2418</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.5554</v>
+        <v>-4.555000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.0655</v>
+        <v>-0.6864</v>
       </c>
       <c r="V24" t="n">
         <v>-4.2969</v>
